--- a/data/trans_dic/P7_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P7_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,68</t>
+          <t>1,64; 4,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,2</t>
+          <t>1,91; 5,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,6</t>
+          <t>1,52; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,88</t>
+          <t>0,78; 7,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,23</t>
+          <t>4,81; 9,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,56</t>
+          <t>3,79; 8,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,04</t>
+          <t>0,97; 3,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 13,41</t>
+          <t>3,16; 12,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,46</t>
+          <t>3,5; 6,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,15</t>
+          <t>3,26; 6,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,55</t>
+          <t>1,57; 3,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,15</t>
+          <t>2,8; 8,68</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,08</t>
+          <t>3,02; 6,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,06</t>
+          <t>4,38; 8,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,12</t>
+          <t>2,84; 6,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,47</t>
+          <t>4,63; 10,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,5; 15,06</t>
+          <t>9,29; 14,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 12,14</t>
+          <t>7,26; 11,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,31</t>
+          <t>4,94; 9,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,24</t>
+          <t>2,16; 6,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,38</t>
+          <t>6,55; 9,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,26</t>
+          <t>6,27; 9,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,85</t>
+          <t>4,3; 6,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,39</t>
+          <t>3,61; 7,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 12,0</t>
+          <t>7,29; 11,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,76</t>
+          <t>7,17; 11,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,86</t>
+          <t>4,98; 8,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 10,5</t>
+          <t>5,8; 10,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 20,4</t>
+          <t>14,76; 20,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,95; 19,82</t>
+          <t>14,37; 19,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,65</t>
+          <t>8,32; 13,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 11,49</t>
+          <t>6,76; 11,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,56</t>
+          <t>12,01; 15,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,32; 15,05</t>
+          <t>11,26; 14,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,22</t>
+          <t>7,24; 10,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,12</t>
+          <t>6,9; 10,08</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 16,4</t>
+          <t>10,3; 16,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,81; 18,13</t>
+          <t>11,97; 18,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,99; 21,18</t>
+          <t>15,31; 21,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 17,13</t>
+          <t>4,83; 17,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,15; 32,01</t>
+          <t>24,44; 32,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,27; 27,57</t>
+          <t>20,5; 27,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,69; 23,38</t>
+          <t>16,51; 22,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 19,74</t>
+          <t>14,41; 19,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 23,25</t>
+          <t>18,12; 23,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 21,86</t>
+          <t>17,16; 21,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,88; 21,28</t>
+          <t>16,75; 21,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,51</t>
+          <t>8,56; 17,71</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,37; 33,52</t>
+          <t>24,47; 33,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,44; 29,21</t>
+          <t>20,57; 28,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,45; 29,18</t>
+          <t>20,94; 29,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,04; 31,36</t>
+          <t>23,76; 30,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,51; 45,2</t>
+          <t>35,4; 45,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,99; 42,37</t>
+          <t>33,12; 42,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,01; 40,17</t>
+          <t>30,69; 40,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,6; 35,34</t>
+          <t>29,51; 35,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,47; 37,93</t>
+          <t>31,66; 37,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,01; 34,76</t>
+          <t>28,27; 34,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,07; 33,56</t>
+          <t>26,89; 33,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,59; 32,43</t>
+          <t>27,64; 32,35</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,42; 43,61</t>
+          <t>32,75; 44,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,47; 42,63</t>
+          <t>31,67; 43,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,55; 35,9</t>
+          <t>25,35; 35,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,01; 31,67</t>
+          <t>24,53; 31,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,26; 63,42</t>
+          <t>53,59; 63,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,97; 53,61</t>
+          <t>42,61; 53,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,4; 51,76</t>
+          <t>41,39; 52,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,2; 41,88</t>
+          <t>12,75; 42,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,26; 52,86</t>
+          <t>45,03; 52,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39,1; 46,8</t>
+          <t>39,26; 46,85</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35,28; 42,35</t>
+          <t>35,39; 42,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,59; 35,62</t>
+          <t>14,12; 35,47</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,87; 61,44</t>
+          <t>48,61; 62,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,0; 63,68</t>
+          <t>50,27; 64,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,51; 50,59</t>
+          <t>39,71; 50,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39,64; 48,9</t>
+          <t>39,45; 48,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,6; 74,39</t>
+          <t>64,36; 75,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,35; 72,29</t>
+          <t>62,17; 72,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,11; 69,16</t>
+          <t>57,76; 68,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>57,18; 63,99</t>
+          <t>56,91; 63,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59,51; 68,11</t>
+          <t>59,81; 68,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,31; 67,36</t>
+          <t>59,41; 66,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51,96; 60,4</t>
+          <t>51,84; 60,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,58; 56,98</t>
+          <t>51,37; 56,95</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,44; 16,89</t>
+          <t>14,38; 16,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,33; 18,12</t>
+          <t>15,41; 18,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,37; 16,95</t>
+          <t>14,47; 17,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,81; 18,25</t>
+          <t>12,65; 18,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,94; 30,19</t>
+          <t>27,03; 30,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,08; 28,21</t>
+          <t>25,05; 28,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,34; 25,42</t>
+          <t>22,44; 25,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,02</t>
+          <t>17,86; 24,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,21; 23,28</t>
+          <t>21,29; 23,29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,7; 22,78</t>
+          <t>20,88; 22,8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,94; 20,91</t>
+          <t>18,93; 20,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,03; 20,9</t>
+          <t>16,65; 20,79</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7822; 23118</t>
+          <t>8114; 23393</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8576; 23581</t>
+          <t>8682; 25637</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5978; 19264</t>
+          <t>6354; 20623</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4102; 31499</t>
+          <t>3107; 29441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22093; 43128</t>
+          <t>22477; 44598</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16585; 36813</t>
+          <t>16286; 36661</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4654; 16001</t>
+          <t>3831; 15535</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10538; 42001</t>
+          <t>9897; 39419</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33876; 62091</t>
+          <t>33690; 61212</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28581; 54365</t>
+          <t>28772; 54368</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11763; 28922</t>
+          <t>12777; 30183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18702; 58131</t>
+          <t>19985; 61893</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21708; 44729</t>
+          <t>22189; 45027</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29004; 55261</t>
+          <t>30013; 56406</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15861; 36117</t>
+          <t>16743; 36932</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18716; 44352</t>
+          <t>19614; 44695</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59399; 94229</t>
+          <t>58114; 91819</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43020; 73987</t>
+          <t>44243; 72989</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28543; 52492</t>
+          <t>27853; 51680</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10900; 31972</t>
+          <t>11055; 31845</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87683; 127666</t>
+          <t>89189; 130969</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78850; 119887</t>
+          <t>81249; 118969</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48686; 79058</t>
+          <t>49596; 78242</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34110; 69177</t>
+          <t>33747; 69115</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45823; 76502</t>
+          <t>46505; 76051</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48680; 80068</t>
+          <t>48806; 78568</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33284; 59269</t>
+          <t>33335; 59969</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29930; 56317</t>
+          <t>31098; 55613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>99485; 140738</t>
+          <t>101819; 141673</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98726; 140312</t>
+          <t>101714; 140467</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53164; 83678</t>
+          <t>54995; 87298</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41010; 67940</t>
+          <t>39989; 67731</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>155799; 206560</t>
+          <t>159434; 209359</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157177; 209053</t>
+          <t>156326; 207432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95787; 135977</t>
+          <t>96323; 134657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75632; 114114</t>
+          <t>77871; 113699</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52293; 85116</t>
+          <t>53447; 85410</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72231; 110874</t>
+          <t>73190; 110533</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96566; 136427</t>
+          <t>98629; 138145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41093; 152061</t>
+          <t>42919; 152128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>124504; 165065</t>
+          <t>126018; 165408</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124882; 169881</t>
+          <t>126310; 170023</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108347; 151776</t>
+          <t>107147; 148814</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101660; 140758</t>
+          <t>102717; 140963</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>185571; 240614</t>
+          <t>187520; 241165</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>210964; 268349</t>
+          <t>210638; 268854</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218277; 275156</t>
+          <t>216552; 274887</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>133810; 280334</t>
+          <t>136972; 283502</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>94252; 129642</t>
+          <t>94642; 128472</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87763; 125442</t>
+          <t>88317; 123834</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97533; 139162</t>
+          <t>99859; 138839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134894; 175983</t>
+          <t>133367; 171307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143456; 182594</t>
+          <t>143023; 182566</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>147709; 189746</t>
+          <t>148297; 191484</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>153733; 199123</t>
+          <t>152139; 198443</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162184; 193623</t>
+          <t>161662; 196574</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>248806; 299904</t>
+          <t>250359; 300405</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>245751; 304889</t>
+          <t>247995; 303273</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>263269; 326382</t>
+          <t>261545; 322030</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>305960; 359736</t>
+          <t>306528; 358788</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>94850; 127598</t>
+          <t>95808; 129004</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>97169; 131635</t>
+          <t>97785; 134057</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85421; 120036</t>
+          <t>84747; 117937</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88404; 116589</t>
+          <t>90325; 117018</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>182662; 217492</t>
+          <t>183764; 219217</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>151712; 189256</t>
+          <t>150435; 187401</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>155566; 194461</t>
+          <t>155507; 195616</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>68160; 254777</t>
+          <t>77574; 255575</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>287655; 335945</t>
+          <t>286171; 336454</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>258818; 309763</t>
+          <t>259860; 310070</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>250487; 300744</t>
+          <t>251272; 304263</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>142516; 347802</t>
+          <t>137845; 346424</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>100464; 128962</t>
+          <t>102032; 130765</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>124936; 159109</t>
+          <t>125596; 160956</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>101187; 129564</t>
+          <t>101687; 129660</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112084; 138273</t>
+          <t>111540; 138396</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>212366; 248396</t>
+          <t>214915; 251289</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>242519; 281186</t>
+          <t>241832; 282487</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>231305; 275286</t>
+          <t>229928; 273875</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>243477; 272475</t>
+          <t>242362; 271074</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>323603; 370393</t>
+          <t>325243; 370908</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>378918; 430287</t>
+          <t>379498; 427667</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>339931; 395141</t>
+          <t>339126; 393201</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>365517; 403739</t>
+          <t>363993; 403536</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>473016; 553293</t>
+          <t>471042; 554950</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>524226; 619743</t>
+          <t>527114; 618993</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>486983; 574639</t>
+          <t>490583; 576108</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>443052; 631334</t>
+          <t>437516; 633711</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>910198; 1020177</t>
+          <t>913456; 1021116</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>891178; 1002317</t>
+          <t>890066; 1002703</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>790681; 899567</t>
+          <t>794259; 899176</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>662368; 891380</t>
+          <t>662805; 891266</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1411771; 1549058</t>
+          <t>1417103; 1550198</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1443221; 1588498</t>
+          <t>1455838; 1589881</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1312133; 1448582</t>
+          <t>1311433; 1441627</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1221613; 1499044</t>
+          <t>1193805; 1491182</t>
         </is>
       </c>
     </row>
